--- a/data/trans_dic/IP31KM16_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM16_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,39</t>
+          <t>7,0; 17,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 17,27</t>
+          <t>5,2; 16,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,31</t>
+          <t>7,47; 14,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,64</t>
+          <t>9,32; 22,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 24,27</t>
+          <t>8,59; 20,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,07</t>
+          <t>10,87; 19,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,34; 25,21</t>
+          <t>3,41; 16,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 16,09</t>
+          <t>9,12; 26,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 16,86</t>
+          <t>7,68; 18,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 23,65</t>
+          <t>8,24; 16,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,01</t>
+          <t>10,23; 20,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 18,21</t>
+          <t>10,3; 16,72</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 18,05</t>
+          <t>7,86; 32,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 35,85</t>
+          <t>7,98; 18,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 26,39</t>
+          <t>9,77; 24,11</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,05; 21,25</t>
+          <t>3,38; 15,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 15,58</t>
+          <t>7,69; 21,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 16,06</t>
+          <t>7,22; 15,91</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,52</t>
+          <t>9,82; 16,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,79; 17,23</t>
+          <t>10,9; 15,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,71</t>
+          <t>11,08; 15,21</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>23334</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4597; 14635</t>
+          <t>8487; 21268</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9330; 23344</t>
+          <t>5220; 16069</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16746; 33887</t>
+          <t>16542; 33060</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27041</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7516; 19272</t>
+          <t>8373; 20580</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9651; 22741</t>
+          <t>8199; 19536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20479; 37549</t>
+          <t>20137; 36847</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12867</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4176; 12626</t>
+          <t>1905; 9050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1805; 10027</t>
+          <t>4742; 13703</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7847; 18951</t>
+          <t>8288; 19703</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>49204</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20988; 50970</t>
+          <t>16262; 32919</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16557; 34052</t>
+          <t>18073; 35826</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43235; 77966</t>
+          <t>38512; 62536</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>37326</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8995; 20853</t>
+          <t>11443; 47570</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13196; 57169</t>
+          <t>9211; 21621</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26815; 72553</t>
+          <t>25498; 62947</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>14787</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5549; 14642</t>
+          <t>2228; 10307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2327; 10756</t>
+          <t>5408; 14990</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9885; 22154</t>
+          <t>9838; 21675</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>115</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>86218</t>
+          <t>83940</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176121</t>
+          <t>164561</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>69441; 106607</t>
+          <t>66338; 110565</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>71721; 126190</t>
+          <t>66515; 95544</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150786; 216428</t>
+          <t>142538; 195565</t>
         </is>
       </c>
     </row>
